--- a/Result/checksun_type/化學品(如光阻劑、靶材等).xlsx
+++ b/Result/checksun_type/化學品(如光阻劑、靶材等).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>318.8</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>348.48</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>367.45</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>348.48</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>367.45</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>259073884.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>228717376.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>228717376.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>293431512.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>481042889.08</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>481042889.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-35024044.91945842</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>259073884</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>259073884.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>314.9</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>350.48</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>368.89</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>350.48</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>368.89</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>86673453.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>261236362.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>261236362.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>300842312.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>491370560.46</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>491370560.46</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-40015166.56547466</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>86673453</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>86673453.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>314.7</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>352.78</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>370.67</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>370.67</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>117241144.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>341116000.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>341116000.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>314298773.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>515382959.98</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>515382959.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-27244752.50387371</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>117241144</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>117241144.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>318.8</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>355.1</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>372.73</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>372.73</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>217244184.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>357191856.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>357191856.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>332478318.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>528510477.64</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>528510477.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-11303386.71930546</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>217244184</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>217244184.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>325.4</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>357.45</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>375.03</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>375.03</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>463354216.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>367149929.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>367149929.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>359440217.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>557019768.38</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>557019768.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>1159073.927195787</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>463354216</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>463354216.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>330.9</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>359.5</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>377.22</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>377.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>421668815.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>358145648.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>358145648.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>348500702.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>576071545.44</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>576071545.4400001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-7447738.360916555</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>421668815</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>421668815.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>338.4</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>361.35</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>378.67</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>378.67</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>486071642.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>340448262.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>340448262.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>351528816.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>590762190.96</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>590762190.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-15010900.86675858</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>486071642</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>486071642.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>347.5</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>363.5</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>380.48</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>380.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>197620426.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>287481546.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>287481546.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>330367833.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>604199364.28</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>604199364.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-32179618.0227201</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>197620426</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>197620426.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>353.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>364.92</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>381.58</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>364.92</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>381.58</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>267034549.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>307764781.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>307764781.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>336027958.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>623949754.94</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>623949754.9400001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-24651597.3161394</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>267034549</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>267034549.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>357.9</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>366.48</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>382.53</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>382.53</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>418332812.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>351730504.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>351730504.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>363412784.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>652574118.58</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>652574118.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-20454095.29544777</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>418332812</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>418332812.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>365.9</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>368.58</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>383.28</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>368.58</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>383.28</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>333181883.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>338855756.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>338855756.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>349472851.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>679806981.48</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>679806981.48</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-29937688.61247945</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>333181883</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>333181883.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>293.7</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>305.35</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>316.68</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>305.35</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>316.68</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>381962.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>423540.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>423540.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>571128.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1027038.7</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1027038.7</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-95536.66314438084</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>381962</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>381962.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>290.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>306.75</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>317.22</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>306.75</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>317.22</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>385514.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>421252.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>421252</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>600889.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1039528.28</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1039528.28</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-98113.18154051743</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>385514</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>385514.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>288.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>308.12</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>317.94</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>308.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>317.94</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>312117.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>438202.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>438202.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>606924.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1049319.12</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1049319.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-98670.45133712271</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>312117</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>312117.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>288.7</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>309.68</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>318.32</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>309.68</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>318.32</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>445977.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>448471.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>448471</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>616039.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1052554.34</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1052554.34</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-88078.642070233</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>445977</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>445977.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>289.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>311.45</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>318.8</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>311.45</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>318.8</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>592131.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>551447.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>551447.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>617315.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1063028.16</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1063028.16</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-84143.9630435966</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>592131</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>592131.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>289.7</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>312.58</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>318.75</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>312.58</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>318.75</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>370521.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>718716.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>718716.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>609804.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1061149.66</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1061149.66</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-91177.20861113025</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>370521</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>370521.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>294.4</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>314.65</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>318.81</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>314.65</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>318.81</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>470267.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>780526.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>780526.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>665770.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1060798.34</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1060798.34</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-74224.44482863788</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>470267</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>470267.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>297.8</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>316.55</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>318.83</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>316.55</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>318.83</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>363459.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>775646.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>775646</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>812744.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1060931.24</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1060931.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-58042.40925262612</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>363459</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>363459.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>302.3</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>318.8</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>318.62</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>318.62</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>960861.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>783608.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>783608</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>878038.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1064507.54</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1064507.54</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-21408.5580993013</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>960861</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>960861.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>307.2</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>321.62</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>318.52</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>321.62</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>318.52</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1428474.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>683183.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>683183.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>960923.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1066873.26</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1066873.26</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-32317.25080529065</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1428474</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1428474.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>311.0</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>323.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>318.39</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>323.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>318.39</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>679570.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>500893.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>500893</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>911225.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1134610.66</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1134610.66</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-96848.30285651505</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>679570</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>679570.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>201.9</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>226.95</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>227.58</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>226.95</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>227.58</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>90663.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>114762.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>114762.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>123500.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>273993.44</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>273993.44</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-31215.27260816598</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>90663</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>90663.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>201.8</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>229.72</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>227.19</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>229.72</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>227.19</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>93169.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>125649.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>125649</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>130618.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>283082.9</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>283082.9</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-30570.17550505494</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>93169</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>93169.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>203.4</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>232.6</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>227.0</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>227</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>90567.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>147137.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>147137.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>171768.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>285167.84</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>285167.84</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-28825.31623257286</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>90567</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>90567.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>207.2</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>235.9</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>226.52</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>235.9</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>226.52</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>188545.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>150672.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>150672.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>224103.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>291936.48</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>291936.48</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-25024.39883500661</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>188545</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>188545.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>212.5</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>239.08</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>226.07</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>239.08</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>226.07</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>110870.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>128416.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>128416</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>221540.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>295295.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>295295</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-29198.43116580459</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>110870</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>110870.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>216.9</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>241.65</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>225.09</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>241.65</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>225.09</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>145094.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>132238.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>132238.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>233985.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>294618.16</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>294618.16</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-25796.21195388012</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>145094</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>145094.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>221.3</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>244.6</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>224.17</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>244.6</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>224.17</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>200610.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>135587.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>135587.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>249984.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>295031.98</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>295031.98</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-23681.46265277802</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>200610</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>200610.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>223.5</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>247.42</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>223.12</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>247.42</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>223.12</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>108244.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>196399.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>196399</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>271350.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>291675.48</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>291675.48</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-25762.76855646149</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>108244</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>108244.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>228.8</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>249.28</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>221.94</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>249.28</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>221.94</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>77262.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>297534.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>297534</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>296942.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>290061.26</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>290061.26</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-17919.60668470713</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>77262</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>77262.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>234.0</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>250.9</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>220.66</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>220.66</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>129983.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>314664.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>314664.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>313434.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>289641.36</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>289641.36</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-2755.603772032773</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>129983</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>129983.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>237.4</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>252.08</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>219.29</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>252.08</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>219.29</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>161837.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>335733.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>335733</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>325527.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>288207.54</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>288207.54</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>13356.99338078895</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>161837</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>161837.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>99.67999999999999</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>104.55</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>114.62</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>114.62</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>11298156.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>9607693.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>9607693.800000001</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>11345070.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>19425437.44</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>19425437.44</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1691198.742789451</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>11298156</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>11298156.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>99.1</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>115.11</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>105</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>115.11</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>8639149.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>9476181.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>9476181.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>10578957.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>19597958.8</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>19597958.8</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1980075.286180986</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>8639149</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>8639149.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>99.38</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>105.44</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>115.7</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>105.44</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>115.7</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>4003587.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>11584639.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>11584639.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>10218452.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>19921033.94</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>19921033.94</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-2037145.480805289</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>4003587</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>4003587.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>100.14</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>105.94</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>116.29</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>105.94</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>116.29</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>13038996.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>14979530.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>14979530.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>11649640.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>20326004.76</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>20326004.76</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-1549251.777382676</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>13038996</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>13038996.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>101.94</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>106.48</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>116.9</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>106.48</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>116.9</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>11058581.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>14273967.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>14273967</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>11459990.4</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>20451780.86</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>20451780.86</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-1765009.887586702</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>11058581</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>11058581.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>103.42</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>107.06</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>117.44</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>107.06</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>117.44</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>10640595.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>13082447.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>13082447</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>11572252.3</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>20461956.14</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>20461956.14</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-1798012.37046436</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>10640595</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>10640595.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>105.0</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>107.75</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>117.98</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>117.98</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>19181437.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>11681732.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>11681732.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>11267888.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>20553347.06</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>20553347.06</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-1736159.832773</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>19181437</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>19181437.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>106.3</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>108.55</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>118.48</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>118.48</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>20978044.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>8852266.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>8852266.199999999</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>11199180.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>20515565.06</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>20515565.06</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-2500883.570614882</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>20978044</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>20978044.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>107.1</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>109.35</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>118.92</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>118.92</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>9511178.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>8319749.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>8319749.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>11464759.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>20864545.1</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>20864545.1</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-3696522.390009895</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>9511178</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>9511178.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>107.0</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>110.02</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>119.33</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>110.02</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>119.33</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>5100981.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>8646013.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>8646013.800000001</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>12611964.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>22452172.42</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>22452172.42</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-4043966.403788129</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>5100981</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>5100981.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>107.3</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>110.55</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>119.72</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>119.72</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>3637022.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>10062057.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>10062057.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>13855229.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>23007709.52</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>23007709.52</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-3923366.516193172</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3637022</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3637022.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>769.8</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>803.35</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>849.62</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>803.35</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>849.62</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>628992.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>781028.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>781028</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1048480.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1729200.38</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1729200.38</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-154123.0698379283</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>628992</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>628992.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>759.8</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>807.6</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>851.0</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>807.6</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>851</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>620926.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>821625.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>821625.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>1092281.9</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1774667.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1774667</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-145063.1254252039</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>620926</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>620926.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>756.4</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>812.4</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>853.2</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>812.4</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>853.2</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1006442.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>918071.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>918071.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1102504.1</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1809073.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1809073</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-126075.3074989831</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1006442</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1006442.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>752.4</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>816.35</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>855.64</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>816.35</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>855.64</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>835135.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1011439.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1011439.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1130299.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1847378.28</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1847378.28</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-135752.4494794183</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>835135</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>835135.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>760.0</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>822.1</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>858.96</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>822.1</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>858.96</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>813645.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1305100.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1305100</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1223286.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1877367.58</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1877367.58</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-126374.3148272038</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>813645</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>813645.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>766.0</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>826.35</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>860.94</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>826.35</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>860.9400000000001</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>831980.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1315932.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1315932.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1215284.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1936249.22</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1936249.22</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-106161.1112230681</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>831980</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>831980.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>781.8</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>833.3</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>862.96</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>833.3</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>862.96</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1103154.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1362938.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1362938.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1257301.1</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1972864.44</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1972864.44</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-75458.10210205056</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1103154</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1103154.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>791.0</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>840.1</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>864.46</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>840.1</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>864.46</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>1473285.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>1286937.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>1286937</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>1300216.9</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1988912.78</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1988912.78</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-57956.08542552381</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>1473285</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>1473285.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>800.8</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>847.7</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>865.74</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>847.7</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>865.74</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>2303436.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>1249159.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>1249159</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>1331639.0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2039810.88</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2039810.88</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-70540.23712243116</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>2303436</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>2303436.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>809.0</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>855.4</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>866.94</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>855.4</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>866.9400000000001</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>867807.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>1141473.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>1141473.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>1356209.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2098887.74</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2098887.74</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-174943.0525064978</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>867807</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>867807.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>815.8</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>860.8</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>866.76</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>860.8</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>866.76</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>1067009.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1114636.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1114636.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>1426058.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>2146767.3</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>2146767.3</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-164024.5726085037</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>1067009</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>1067009.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>153.5</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>164.42</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>173.67</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>164.42</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>173.67</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>986262927.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>511754625.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>511754625.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>501131253.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1082924116.42</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1082924116.42</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-36210668.31905305</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>986262927</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>986262927.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>151.7</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>165.55</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>173.06</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>165.55</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>173.06</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>250013752.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>372455254.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>372455254</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>552080309.1</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1087864603.14</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1087864603.14</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-87444448.69656801</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>250013752</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>250013752.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>151.4</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>166.82</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>172.87</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>166.82</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>172.87</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>184281007.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>420756005.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>420756005</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>659541126.6</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1095948778.6</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1095948778.6</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-78628707.31814063</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>184281007</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>184281007.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>153.6</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>168.42</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>172.48</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>168.42</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>172.48</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>544245519.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>472004107.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>472004107.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>697496232.0</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1131916420.52</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1131916420.52</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-56183828.8375963</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>544245519</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>544245519.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>156.0</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>169.78</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>172.12</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>169.78</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>172.12</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>593969923.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>467688609.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>467688609.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>666661200.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1123257424.94</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1123257424.94</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-60680777.69261885</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>593969923</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>593969923.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>158.3</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>171.55</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>171.59</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>171.55</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>171.59</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>289766069.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>490507881.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>490507881.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>633681458.9</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1113208806.46</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1113208806.46</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-70265434.42505753</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>289766069</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>289766069.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>163.7</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>174.5</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>171.23</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>171.23</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>491517507.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>731705364.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>731705364.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>661541061.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1110250931.48</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1110250931.48</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-48855051.31336081</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>491517507</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>491517507.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>167.7</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>177.42</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>170.91</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>177.42</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>170.91</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>440521520.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>898326248.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>898326248.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>658310707.8</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1103331078.56</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1103331078.56</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-38140191.9640311</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>440521520</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>440521520.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>168.0</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>179.65</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>170.45</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>179.65</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>170.45</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>522668030.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>922988356.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>922988356.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>644511613.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>1097913006.62</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>1097913006.62</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-16007244.57341611</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>522668030</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>522668030.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>169.4</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>181.78</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>170.07</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>181.78</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>170.07</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>708066282.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>865633791.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>865633791.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>648173719.0</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>1093088449.18</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>1093088449.18</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>7381527.219370127</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>708066282</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>708066282.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>169.1</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>183.22</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>169.49</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>169.49</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>1495753482.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>776855036.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>776855036.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>628030142.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1082454863.8</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1082454863.8</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>20666333.95123005</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1495753482</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1495753482.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>13.76</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>14.76</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>14.76</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>2035612.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1742622.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1742622</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>3623289.3</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>4611435.6</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>4611435.6</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-730389.703553101</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>2035612</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>2035612.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>13.67</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>14.79</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>14.79</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>1130737.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>2006755.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>2006755.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>3720577.0</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>4673421.5</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>4673421.5</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-747155.6479886342</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>1130737</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>1130737.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>13.62</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>14.83</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>14.83</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>1144970.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>3164286.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>3164286.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>3982209.1</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>4788813.84</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>4788813.84</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-647471.9740398023</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>1144970</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>1144970.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>13.61</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>14.07</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>14.87</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>14.87</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1478293.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>5213697.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>5213697.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>4243254.9</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>4943161.66</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>4943161.66</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-483467.6907543349</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1478293</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1478293.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>13.69</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>14.14</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>14.92</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>2923498.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>5645358.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>5645358.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>4277998.2</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>5044708.62</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>5044708.62</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-267622.3328195838</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>2923498</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>2923498.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>13.77</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>14.97</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>3356279.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>5503956.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>5503956.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>4189681.6</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>5444701.66</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>5444701.66</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-104557.2738835253</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>3356279</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>3356279.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>13.9</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>15.02</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>6918391.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>5434398.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>5434398.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>4271440.4</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>5617822.56</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>5617822.56</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>85757.60580668412</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>6918391</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>6918391.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>11392026.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>4800132.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>4800132</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>4131465.3</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>5585222.04</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>5585222.04</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-27081.62341468502</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>11392026</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>11392026.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>15.1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>3636599.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>3272812.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>3272812.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>4238385.9</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>5473025.66</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>5473025.66</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-666631.3571804017</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>3636599</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>3636599.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,21 +33307,17 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
+      <c r="AM77" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AO77" t="inlineStr">
         <is>
           <t>15.13</t>
         </is>
       </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>15.13</t>
-        </is>
-      </c>
       <c r="AP77" t="inlineStr">
         <is>
           <t>0.55</t>
@@ -33812,20 +33358,16 @@
           <t>2216488.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>2910637.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>2910637.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>4261119.7</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>5563641.26</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>5563641.26</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-725526.9640892674</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>2216488</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>2216488.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>13.98</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>14.52</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>15.16</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>3008489.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>2875406.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>2875406.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>6471977.8</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>6141477.24</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>6141477.24</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-631597.118098746</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>3008489</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>3008489.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>41.79</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>43.65</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>47.07</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>47.07</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>18788.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>11702.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>11702.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>11910.8</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>21841.68</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>21841.68</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-835.0067717372658</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>18788</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>18788.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>41.26000000000001</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>47.26</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>47.26</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>10470.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>9823.8</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>9823.799999999999</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>12026.4</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>22264.28</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>22264.28</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-1547.487138612682</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>10470</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>10470.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>41.17</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>43.97</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>47.52</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>5468.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>11849.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>11849.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>12661.3</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>22603.46</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>22603.46</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-1618.834550627105</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>5468</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>5468.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>41.75</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>44.22</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>12727.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>12695.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>12695.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>17521.5</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>23333.98</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>23333.98</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-1127.015333839599</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>12727</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>12727.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>42.59</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>44.56</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>48.12</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>48.12</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>11061.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>11822.4</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>11822.4</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>17187.6</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>24177.16</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>24177.16</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-1161.915905077462</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>11061</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>11061.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>43.29</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>44.84</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>48.39</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>48.39</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>9393.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>12118.8</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>12118.8</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>17166.1</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>25730.42</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>25730.42</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-991.7768673787868</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>9393</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>9393.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>44.42</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>48.65</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>20598.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>14229.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>14229</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>17330.2</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>25955.2</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>25955.2</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-534.58621111715</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>20598</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>20598.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>45.3</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>45.46</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>48.9</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>9697.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>13473.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>13473.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>17029.4</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>26019.26</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>26019.26</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-1062.900051774917</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>9697</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>9697.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>45.48</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>45.64</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>49.1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>8363.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>22347.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>22347.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>17369.8</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>26332.84</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>26332.84</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-611.7091080083301</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>8363</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>8363.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>45.25</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>45.78</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>49.3</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>12543.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>22552.8</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>22552.8</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>18149.7</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>27319.1</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>27319.1</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>197.6247083728013</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>12543</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>12543.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>45.05</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>49.54</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>49.54</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>19944.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>22213.4</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>22213.4</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>18422.7</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>29048.06</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>29048.06</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>898.9007064753896</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>19944</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>19944.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>105.3</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>99.52</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>96.51</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>96.51000000000001</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>85287514.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>151213318.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>151213318.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>151318475.9</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>91042396.88</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>91042396.88</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>2711461.138127059</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>85287514</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>85287514.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>104.3</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>98.73</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>96.33</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>96.33</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>217044233.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>151864079.6</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>151864079.6</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>171702620.0</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>90320956.04</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>90320956.04000001</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>9994869.517893165</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>217044233</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>217044233.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>102.9</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>97.92</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>96.16</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>96.16</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>159600272.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>134412279.8</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>134412279.8</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>168766249.4</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>87040848.98</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>87040848.98</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>5925987.684777111</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>159600272</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>159600272.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>102.7</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>97.32</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>96.05</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>96.05</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>152247091.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>131651785.8</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>131651785.8</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>188252615.4</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>84978583.08</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>84978583.08</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>6056367.041583598</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>152247091</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>152247091.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>102.9</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>96.76</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>95.96</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>95.95999999999999</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>141887484.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>132448333.4</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>132448333.4</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>196531473.3</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>82918302.5</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>82918302.5</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>6814165.264107674</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>141887484</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>141887484.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>102.9</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>96.18</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>95.82</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>96.18000000000001</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>95.81999999999999</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>88541318.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>151423633.0</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>151423633</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>196000867.3</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>80594523.88</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>80594523.88</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>8763329.00113827</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>88541318</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>88541318.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>103.3</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>95.75</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>95.74</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>95.73999999999999</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>129785234.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>191541160.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>191541160.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>194097538.2</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>79445022.76</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>79445022.76000001</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>16950533.2325699</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>129785234</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>129785234.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>103.4</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>95.38</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>95.67</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>95.67</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>145797802.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>203120219.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>203120219</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>186910809.6</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>77335277.14</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>77335277.14</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>23622172.09059471</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>145797802</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>145797802.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>102.38</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>95.53</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>95.53</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>156229829.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>244853445.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>244853445</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>177136934.0</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>75407300.22</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>75407300.22</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>30593803.45596609</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>156229829</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>156229829.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>100.68</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>94.2</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>95.39</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>95.39</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>236763982.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>260614613.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>260614613.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>164971086.0</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>73504886.64</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>73504886.64</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>38342923.81878352</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>236763982</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>236763982.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>98.6</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>93.46</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>95.28</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>95.28</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>289128955.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>240578101.6</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>240578101.6</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>146043684.0</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>69868524.62</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>69868524.62</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>39415046.37928045</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>289128955</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>289128955.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>57.16</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>58.14</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>60.07</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>60.07</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>162030.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>209836.2</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>209836.2</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>215755.9</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>550120.9</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>550120.9</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-38160.02218378661</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>162030</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>162030.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>57.23999999999999</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>58.29</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>60.05</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>60.05</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>199284.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>213119.2</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>213119.2</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>251269.4</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>555483.94</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>555483.9399999999</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-36671.78477886959</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>199284</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>199284.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>57.36</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>60.09</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>136228.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>212208.6</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>212208.6</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>325088.9</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>556448.64</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>556448.64</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-37227.52474402849</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>136228</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>136228.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>57.62</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>273475.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>241628.6</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>241628.6</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>353601.2</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>558552.82</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>558552.8199999999</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-29935.8845248259</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>273475</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>58.17999999999999</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>60.16</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>278164.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>235377.2</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>235377.2</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>343709.9</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>560862.08</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>560862.08</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-33155.15262150689</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>278164</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>278164.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>58.38000000000001</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>59.01</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>60.14</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>178445.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>221675.6</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>221675.6</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>333361.3</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>566147.36</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>566147.36</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-37072.38730885455</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>178445</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>59.24</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>194731.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>289419.6</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>341561.2</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>568481.84</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-30660.24445832073</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>194731</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>194731.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>59.73999999999999</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>59.51</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>60.1</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>283328.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>437969.2</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>437969.2</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>356514.8</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>570563.3</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>570563.3</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-22149.96022690379</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>283328</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>283328.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>60.12</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>59.74</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>60.09</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>242218.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>465573.8</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>465573.8</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>341803.5</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>579417.88</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>579417.88</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-18693.87703106157</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>242218</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>242218.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>59.72000000000001</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>59.98</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>60.1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>209656.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>452042.6</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>452042.6</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>332281.8</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>596784.86</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>596784.86</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-8684.334000177623</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>209656</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>209656.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>59.14</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>60.08</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>60.08</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>517165.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>445047.0</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>445047</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>339942.5</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>643736.64</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>643736.64</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>9413.953686805733</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>517165</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>517165.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>134.8</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>139.38</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>139.96</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>139.38</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>139.96</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>37172766.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>30181997.8</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>30181997.8</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>53188038.5</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>84757850.72</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>84757850.72</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-11890583.12028044</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>37172766</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>37172766.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>133.5</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>139.96</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>139.96</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>13634899.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>34643442.4</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>34643442.4</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>53592667.9</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>88162538.74</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>88162538.73999999</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-12517821.34918105</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>13634899</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>13634899.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>133.3</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>139.72</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>140.13</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>139.72</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>140.13</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>31524306.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>49427449.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>49427449</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>56359500.5</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>89876362.32</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>89876362.31999999</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-10444896.59228258</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>31524306</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>31524306.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>134.1</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>140.02</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>140.3</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>140.02</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>140.3</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>36163712.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>62637590.6</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>62637590.6</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>92096261.0</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>92202525.62</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>92202525.62</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-9027265.668417536</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>36163712</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>36163712.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>135.9</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>140.5</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>140.51</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>140.51</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>32414306.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>67592316.4</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>67592316.40000001</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>94150971.3</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>97218297.64</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>97218297.64</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-7176755.503309697</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>32414306</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>32414306.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>137.7</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>140.9</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>140.79</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>140.79</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>59479989.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>76194079.2</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>76194079.2</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>94900125.9</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>99838644.16</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>99838644.16</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>-3875134.785180286</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>59479989</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>59479989.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>139.6</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>141.5</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>141.1</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>141.1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>87554932.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>72541893.4</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>72541893.40000001</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>93622235.4</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>105440078.84</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>105440078.84</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>-1920030.695524707</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>87554932</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>87554932.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>140.9</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>142.1</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>141.49</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>141.49</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>97575014.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>63291552.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>63291552</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>89977049.0</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>110816429.32</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>110816429.32</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>-2066481.935462266</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>97575014</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>97575014.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>141.6</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>142.5</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>141.7</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>141.7</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>60937341.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>121554931.4</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>121554931.4</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>87363166.2</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>129046955.98</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>129046955.98</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>-3275475.280535117</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>60937341</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>60937341.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>141.3</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>142.88</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>141.95</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>142.88</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>141.95</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>75423120.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>120709626.2</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>120709626.2</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>94233663.1</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>153864850.94</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>153864850.94</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-960162.4063343853</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>75423120</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>75423120.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>141.3</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>143.02</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>141.9</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>143.02</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>141.9</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>41219060.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>113606172.6</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>113606172.6</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>94451491.9</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>155796011.12</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>155796011.12</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>829671.1784643084</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>41219060</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>41219060.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,21 +53087,17 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
+      <c r="AM123" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AO123" t="inlineStr">
         <is>
           <t>39.53</t>
         </is>
       </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
       <c r="AP123" t="inlineStr">
         <is>
           <t>-19.58</t>
@@ -53868,20 +53138,16 @@
           <t>201657416.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>252360977.6</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>252360977.6</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>282417854.9</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>423553251.3</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>423553251.3</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>-36974729.3629033</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>201657416</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>201657416.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>39.04000000000001</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>39.71</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>40.26</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>40.26</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>195613562.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>255801795.6</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>255801795.6</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>285762642.3</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>457544220.78</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>457544220.78</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-35925485.46414912</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>195613562</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>195613562.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>39.16</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>39.91</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>40.4</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>188357162.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>277240412.8</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>277240412.8</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>297413036.7</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>528814161.92</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>528814161.92</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-32495956.77078068</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>188357162</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>188357162.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>39.25</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>39.94</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>40.53</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>40.53</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>355837208.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>346026858.8</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>346026858.8</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>290442567.6</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>558638708.96</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>558638708.96</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>-25658588.75272644</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>355837208</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>355837208.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>39.93</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>40.66</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>40.66</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>320339540.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>322944767.0</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>322944767</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>273188557.9</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>613979125.7</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>613979125.7</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>-32918832.62862295</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>320339540</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>320339540.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>40.74</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>218861506.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>312474732.2</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>312474732.2</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>262014209.7</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>631667121.94</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>631667121.9400001</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>-38311615.42888141</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>218861506</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>218861506.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>39.55</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>39.83</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>40.77</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>40.77</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>302806648.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>315723489.0</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>315723489</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>267936291.1</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>654424013.3</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>654424013.3</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>-33774672.37821913</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>302806648</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>302806648.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>39.57000000000001</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>40.87</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>40.87</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>532289392.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>317585660.6</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>317585660.6</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>263274442.8</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>673739372.28</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>673739372.28</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>-35081209.22090816</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>532289392</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>532289392.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>39.51000000000001</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>39.76</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>41</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>240426749.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>234858276.4</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>234858276.4</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>236240878.5</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>679732391.62</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>679732391.62</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>-60282226.95257431</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>240426749</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>240426749.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>39.5</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>41.14</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>267989366.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>223432348.8</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>223432348.8</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>270578244.9</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>693037521.34</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>693037521.34</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>-62859746.71379119</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>267989366</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>267989366.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>39.52</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>39.72</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>41.21</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>41.21</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>235105290.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>211553687.2</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>211553687.2</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>317718579.4</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>694915339.42</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>694915339.42</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>-67250064.3828941</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>235105290</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>235105290.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58425,7 +57633,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -58609,15 +57817,11 @@
           <t>17.68</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>19.05</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>19.05</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58664,20 +57868,16 @@
           <t>27545944.0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>32561534.6</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>32561534.6</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>51519003.4</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>82205412.14</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>82205412.14</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57894,10 @@
           <t>-5110856.075542763</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>27545944</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>27545944.0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
@@ -58861,7 +58063,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -59045,15 +58247,11 @@
           <t>17.62</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>19.1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -59100,20 +58298,16 @@
           <t>41265824.0</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>34157774.2</t>
-        </is>
+      <c r="AX135" t="n">
+        <v>34157774.2</v>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>52942274.3</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>97003735.86</t>
-        </is>
+      <c r="AZ135" t="n">
+        <v>97003735.86</v>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
@@ -59130,8 +58324,10 @@
           <t>-4541392.253075995</t>
         </is>
       </c>
-      <c r="BD135" t="n">
-        <v>41265824</v>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>41265824.0</t>
+        </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
@@ -59297,7 +58493,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -59481,15 +58677,11 @@
           <t>17.62</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>18.49</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>19.18</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>19.18</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59536,20 +58728,16 @@
           <t>24630282.0</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>36415219.6</t>
-        </is>
+      <c r="AX136" t="n">
+        <v>36415219.6</v>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>51242747.6</t>
         </is>
       </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>125077625.38</t>
-        </is>
+      <c r="AZ136" t="n">
+        <v>125077625.38</v>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
@@ -59566,8 +58754,10 @@
           <t>-5035667.069085032</t>
         </is>
       </c>
-      <c r="BD136" t="n">
-        <v>24630282</v>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>24630282.0</t>
+        </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
@@ -59733,7 +58923,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59917,15 +59107,11 @@
           <t>17.85</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>18.61</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>19.23</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>19.23</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59972,20 +59158,16 @@
           <t>41343469.0</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>45429471.0</t>
-        </is>
+      <c r="AX137" t="n">
+        <v>45429471</v>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>51469072.0</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>135512407.44</t>
-        </is>
+      <c r="AZ137" t="n">
+        <v>135512407.44</v>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
@@ -60002,8 +59184,10 @@
           <t>-3779549.196630619</t>
         </is>
       </c>
-      <c r="BD137" t="n">
-        <v>41343469</v>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>41343469.0</t>
+        </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
@@ -60169,7 +59353,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -60353,15 +59537,11 @@
           <t>18.24</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>19.26</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -60408,20 +59588,16 @@
           <t>28022154.0</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>60780539.6</t>
-        </is>
+      <c r="AX138" t="n">
+        <v>60780539.6</v>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>49039304.3</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>137304471.88</t>
-        </is>
+      <c r="AZ138" t="n">
+        <v>137304471.88</v>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
@@ -60438,8 +59614,10 @@
           <t>-3640809.800387502</t>
         </is>
       </c>
-      <c r="BD138" t="n">
-        <v>28022154</v>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>28022154.0</t>
+        </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
@@ -60605,7 +59783,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -60789,15 +59967,11 @@
           <t>18.52</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>18.78</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>19.28</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60844,20 +60018,16 @@
           <t>35527142.0</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>70476472.2</t>
-        </is>
+      <c r="AX139" t="n">
+        <v>70476472.2</v>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>48367971.6</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>140530781.3</t>
-        </is>
+      <c r="AZ139" t="n">
+        <v>140530781.3</v>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
@@ -60874,8 +60044,10 @@
           <t>-1885297.991454914</t>
         </is>
       </c>
-      <c r="BD139" t="n">
-        <v>35527142</v>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>35527142.0</t>
+        </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
@@ -61041,7 +60213,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -61225,15 +60397,11 @@
           <t>18.76</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>19.29</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -61280,20 +60448,16 @@
           <t>52553051.0</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>71726774.4</t>
-        </is>
+      <c r="AX140" t="n">
+        <v>71726774.40000001</v>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>47912479.7</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>140353737.84</t>
-        </is>
+      <c r="AZ140" t="n">
+        <v>140353737.84</v>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
@@ -61310,8 +60474,10 @@
           <t>-114197.7647135556</t>
         </is>
       </c>
-      <c r="BD140" t="n">
-        <v>52553051</v>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>52553051.0</t>
+        </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
@@ -61477,7 +60643,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -61661,15 +60827,11 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>19.29</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61716,20 +60878,16 @@
           <t>69701539.0</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>66070275.6</t>
-        </is>
+      <c r="AX141" t="n">
+        <v>66070275.6</v>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>46567948.0</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>139781443.8</t>
-        </is>
+      <c r="AZ141" t="n">
+        <v>139781443.8</v>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
@@ -61746,8 +60904,10 @@
           <t>595819.372228153</t>
         </is>
       </c>
-      <c r="BD141" t="n">
-        <v>69701539</v>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>69701539.0</t>
+        </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
@@ -61913,7 +61073,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -62097,15 +61257,11 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>19.28</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -62152,20 +61308,16 @@
           <t>118098812.0</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>57508673.0</t>
-        </is>
+      <c r="AX142" t="n">
+        <v>57508673</v>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>42493200.7</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
-        <is>
-          <t>139366944.98</t>
-        </is>
+      <c r="AZ142" t="n">
+        <v>139366944.98</v>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
@@ -62182,8 +61334,10 @@
           <t>-248487.6954346895</t>
         </is>
       </c>
-      <c r="BD142" t="n">
-        <v>118098812</v>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>118098812.0</t>
+        </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
@@ -62349,7 +61503,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -62533,15 +61687,11 @@
           <t>18.75</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>18.94</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>19.26</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62588,20 +61738,16 @@
           <t>76501817.0</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>37298069.0</t>
-        </is>
+      <c r="AX143" t="n">
+        <v>37298069</v>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>33598142.9</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
-        <is>
-          <t>138751251.62</t>
-        </is>
+      <c r="AZ143" t="n">
+        <v>138751251.62</v>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
@@ -62618,8 +61764,10 @@
           <t>-6631188.195830375</t>
         </is>
       </c>
-      <c r="BD143" t="n">
-        <v>76501817</v>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>76501817.0</t>
+        </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
@@ -62785,7 +61933,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -62969,15 +62117,11 @@
           <t>18.65</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>18.94</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>19.25</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -63024,20 +62168,16 @@
           <t>41778653.0</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>26259471.0</t>
-        </is>
+      <c r="AX144" t="n">
+        <v>26259471</v>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>33359343.4</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>138380212.08</t>
-        </is>
+      <c r="AZ144" t="n">
+        <v>138380212.08</v>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
@@ -63054,8 +62194,10 @@
           <t>-11055682.72511597</t>
         </is>
       </c>
-      <c r="BD144" t="n">
-        <v>41778653</v>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>41778653.0</t>
+        </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
